--- a/artfynd/A 20163-2026 artfynd.xlsx
+++ b/artfynd/A 20163-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1560,6 +1560,319 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133342615</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lappnäsholmen, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>721153</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7074780</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133342617</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91948</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lappnäsholmen, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>721192</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7074785</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133342616</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57136</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lappnäsholmen, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>721200</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7074758</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färsk spillning</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20163-2026 artfynd.xlsx
+++ b/artfynd/A 20163-2026 artfynd.xlsx
@@ -1565,7 +1565,7 @@
         <v>133342615</v>
       </c>
       <c r="B9" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>133342617</v>
       </c>
       <c r="B10" t="n">
-        <v>91948</v>
+        <v>91967</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>133342616</v>
       </c>
       <c r="B11" t="n">
-        <v>57136</v>
+        <v>57143</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 20163-2026 artfynd.xlsx
+++ b/artfynd/A 20163-2026 artfynd.xlsx
@@ -1565,7 +1565,7 @@
         <v>133342615</v>
       </c>
       <c r="B9" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>133342617</v>
       </c>
       <c r="B10" t="n">
-        <v>91967</v>
+        <v>91977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>133342616</v>
       </c>
       <c r="B11" t="n">
-        <v>57143</v>
+        <v>57153</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 20163-2026 artfynd.xlsx
+++ b/artfynd/A 20163-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1873,6 +1873,871 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133210656</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lappnäsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>721193</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7074784</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133210653</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91957</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lappnäsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>721113</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7074774</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133210654</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92389</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lappnäsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>721028</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7074796</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133210655</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91957</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lappnäsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>721025</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7074794</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133210658</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91977</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lappnäsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>721193</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7074784</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133210660</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91957</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lappnäsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>721211</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7074788</v>
+      </c>
+      <c r="S17" t="n">
+        <v>16</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133210651</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lappnäsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>721116</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7074774</v>
+      </c>
+      <c r="S18" t="n">
+        <v>48</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>4,5 cm stort i diameter vilket stämmer bra överens med måttet på bohål för tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133210659</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92389</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lappnäsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>721211</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7074776</v>
+      </c>
+      <c r="S19" t="n">
+        <v>14</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20163-2026 artfynd.xlsx
+++ b/artfynd/A 20163-2026 artfynd.xlsx
@@ -1875,10 +1875,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133210656</v>
+        <v>133210653</v>
       </c>
       <c r="B12" t="n">
-        <v>57972</v>
+        <v>91957</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,21 +1886,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1910,13 +1910,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721193</v>
+        <v>721113</v>
       </c>
       <c r="R12" t="n">
-        <v>7074784</v>
+        <v>7074774</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1982,10 +1982,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133210653</v>
+        <v>133210656</v>
       </c>
       <c r="B13" t="n">
-        <v>91957</v>
+        <v>57972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2017,13 +2017,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>721113</v>
+        <v>721193</v>
       </c>
       <c r="R13" t="n">
-        <v>7074774</v>
+        <v>7074784</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2303,10 +2303,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133210658</v>
+        <v>133210651</v>
       </c>
       <c r="B16" t="n">
-        <v>91977</v>
+        <v>57975</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,33 +2314,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lappnäsberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721193</v>
+        <v>721116</v>
       </c>
       <c r="R16" t="n">
-        <v>7074784</v>
+        <v>7074774</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2369,7 +2381,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2379,7 +2391,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>4,5 cm stort i diameter vilket stämmer bra överens med måttet på bohål för tretåig hackspett</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,10 +2423,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133210660</v>
+        <v>133210658</v>
       </c>
       <c r="B17" t="n">
-        <v>91957</v>
+        <v>91977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,23 +2434,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2441,13 +2454,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721211</v>
+        <v>721193</v>
       </c>
       <c r="R17" t="n">
-        <v>7074788</v>
+        <v>7074784</v>
       </c>
       <c r="S17" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2476,7 +2489,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2486,7 +2499,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,10 +2526,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133210651</v>
+        <v>133210660</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>91957</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,45 +2537,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lappnäsberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721116</v>
+        <v>721211</v>
       </c>
       <c r="R18" t="n">
-        <v>7074774</v>
+        <v>7074788</v>
       </c>
       <c r="S18" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2591,7 +2596,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2601,12 +2606,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>4,5 cm stort i diameter vilket stämmer bra överens med måttet på bohål för tretåig hackspett</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 20163-2026 artfynd.xlsx
+++ b/artfynd/A 20163-2026 artfynd.xlsx
@@ -2303,10 +2303,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133210651</v>
+        <v>133210658</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>91977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,45 +2314,33 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lappnäsberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721116</v>
+        <v>721193</v>
       </c>
       <c r="R16" t="n">
-        <v>7074774</v>
+        <v>7074784</v>
       </c>
       <c r="S16" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2381,7 +2369,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2391,12 +2379,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>4,5 cm stort i diameter vilket stämmer bra överens med måttet på bohål för tretåig hackspett</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2423,10 +2406,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133210658</v>
+        <v>133210660</v>
       </c>
       <c r="B17" t="n">
-        <v>91977</v>
+        <v>91957</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2434,19 +2417,23 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2454,13 +2441,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721193</v>
+        <v>721211</v>
       </c>
       <c r="R17" t="n">
-        <v>7074784</v>
+        <v>7074788</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2489,7 +2476,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2499,7 +2486,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2526,10 +2513,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133210660</v>
+        <v>133210651</v>
       </c>
       <c r="B18" t="n">
-        <v>91957</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2537,37 +2524,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lappnäsberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721211</v>
+        <v>721116</v>
       </c>
       <c r="R18" t="n">
-        <v>7074788</v>
+        <v>7074774</v>
       </c>
       <c r="S18" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2596,7 +2591,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2606,7 +2601,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>4,5 cm stort i diameter vilket stämmer bra överens med måttet på bohål för tretåig hackspett</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 20163-2026 artfynd.xlsx
+++ b/artfynd/A 20163-2026 artfynd.xlsx
@@ -1675,7 +1675,7 @@
         <v>133342617</v>
       </c>
       <c r="B10" t="n">
-        <v>91977</v>
+        <v>91979</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>133210653</v>
       </c>
       <c r="B12" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>133210654</v>
       </c>
       <c r="B14" t="n">
-        <v>92389</v>
+        <v>92391</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>133210655</v>
       </c>
       <c r="B15" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>133210658</v>
       </c>
       <c r="B16" t="n">
-        <v>91977</v>
+        <v>91979</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>133210660</v>
       </c>
       <c r="B17" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>133210659</v>
       </c>
       <c r="B19" t="n">
-        <v>92389</v>
+        <v>92391</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 20163-2026 artfynd.xlsx
+++ b/artfynd/A 20163-2026 artfynd.xlsx
@@ -1875,10 +1875,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133210653</v>
+        <v>133210656</v>
       </c>
       <c r="B12" t="n">
-        <v>91960</v>
+        <v>57972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,21 +1886,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1910,13 +1910,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721113</v>
+        <v>721193</v>
       </c>
       <c r="R12" t="n">
-        <v>7074774</v>
+        <v>7074784</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1982,10 +1982,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133210656</v>
+        <v>133210653</v>
       </c>
       <c r="B13" t="n">
-        <v>57972</v>
+        <v>91960</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2017,13 +2017,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>721193</v>
+        <v>721113</v>
       </c>
       <c r="R13" t="n">
-        <v>7074784</v>
+        <v>7074774</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2303,10 +2303,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133210658</v>
+        <v>133210660</v>
       </c>
       <c r="B16" t="n">
-        <v>91980</v>
+        <v>91960</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,19 +2314,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2334,13 +2338,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721193</v>
+        <v>721211</v>
       </c>
       <c r="R16" t="n">
-        <v>7074784</v>
+        <v>7074788</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2369,7 +2373,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2379,7 +2383,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,10 +2410,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133210660</v>
+        <v>133210658</v>
       </c>
       <c r="B17" t="n">
-        <v>91960</v>
+        <v>91980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,23 +2421,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2441,13 +2441,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721211</v>
+        <v>721193</v>
       </c>
       <c r="R17" t="n">
-        <v>7074788</v>
+        <v>7074784</v>
       </c>
       <c r="S17" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 20163-2026 artfynd.xlsx
+++ b/artfynd/A 20163-2026 artfynd.xlsx
@@ -1675,7 +1675,7 @@
         <v>133342617</v>
       </c>
       <c r="B10" t="n">
-        <v>91980</v>
+        <v>91987</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1875,10 +1875,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133210656</v>
+        <v>133210653</v>
       </c>
       <c r="B12" t="n">
-        <v>57972</v>
+        <v>91967</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,21 +1886,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1910,13 +1910,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721193</v>
+        <v>721113</v>
       </c>
       <c r="R12" t="n">
-        <v>7074784</v>
+        <v>7074774</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1982,10 +1982,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133210653</v>
+        <v>133210656</v>
       </c>
       <c r="B13" t="n">
-        <v>91960</v>
+        <v>57972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2017,13 +2017,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>721113</v>
+        <v>721193</v>
       </c>
       <c r="R13" t="n">
-        <v>7074774</v>
+        <v>7074784</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2092,7 +2092,7 @@
         <v>133210654</v>
       </c>
       <c r="B14" t="n">
-        <v>92392</v>
+        <v>92399</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>133210655</v>
       </c>
       <c r="B15" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2303,10 +2303,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133210660</v>
+        <v>133210658</v>
       </c>
       <c r="B16" t="n">
-        <v>91960</v>
+        <v>91987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,23 +2314,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2338,13 +2334,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721211</v>
+        <v>721193</v>
       </c>
       <c r="R16" t="n">
-        <v>7074788</v>
+        <v>7074784</v>
       </c>
       <c r="S16" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2373,7 +2369,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2383,7 +2379,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2410,10 +2406,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133210658</v>
+        <v>133210660</v>
       </c>
       <c r="B17" t="n">
-        <v>91980</v>
+        <v>91967</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2421,19 +2417,23 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2441,13 +2441,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721193</v>
+        <v>721211</v>
       </c>
       <c r="R17" t="n">
-        <v>7074784</v>
+        <v>7074788</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2636,7 +2636,7 @@
         <v>133210659</v>
       </c>
       <c r="B19" t="n">
-        <v>92392</v>
+        <v>92399</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 20163-2026 artfynd.xlsx
+++ b/artfynd/A 20163-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>59474108</v>
+        <v>100976996</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hummelholm, Ång</t>
+          <t>Lappnäsholmen, Hummelholm, Nordmaling, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>721011.1441440975</v>
+        <v>721175</v>
       </c>
       <c r="R2" t="n">
-        <v>7074785.192873186</v>
+        <v>7074778</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-04-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>04:30</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-04-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,31 +756,45 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Carl Jansson, Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100976999</v>
+        <v>133210653</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,37 +802,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lappnäsholmen, Hummelholm, Nordmaling, Ång</t>
+          <t>Lappnäsberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>721111.6628416192</v>
+        <v>721113</v>
       </c>
       <c r="R3" t="n">
-        <v>7074773.145832566</v>
+        <v>7074774</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,22 +856,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-05-18</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-05-18</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,50 +882,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carl Jansson, Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100976996</v>
+        <v>133210655</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,17 +929,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lappnäsholmen, Hummelholm, Nordmaling, Ång</t>
+          <t>Lappnäsberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721174.5067786613</v>
+        <v>721025</v>
       </c>
       <c r="R4" t="n">
-        <v>7074778.006523434</v>
+        <v>7074794</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,22 +963,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-18</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-05-18</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,50 +989,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carl Jansson, Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100976997</v>
+        <v>133210660</v>
       </c>
       <c r="B5" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,42 +1016,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lappnäsholmen, Hummelholm, Nordmaling, Ång</t>
+          <t>Lappnäsberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>721204.9115324395</v>
+        <v>721211</v>
       </c>
       <c r="R5" t="n">
-        <v>7074763.257066991</v>
+        <v>7074788</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1133,22 +1070,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-18</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-05-18</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,31 +1100,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carl Jansson, Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100976994</v>
+        <v>133210654</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,37 +1123,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lappnäsholmen, Hummelholm, Nordmaling, Ång</t>
+          <t>Lappnäsberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>721051.9741842593</v>
+        <v>721028</v>
       </c>
       <c r="R6" t="n">
-        <v>7074837.386319377</v>
+        <v>7074796</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1249,22 +1177,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-05-18</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-05-18</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,50 +1203,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carl Jansson, Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>100976995</v>
+        <v>133210659</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92406</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,37 +1230,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lappnäsholmen, Hummelholm, Nordmaling, Ång</t>
+          <t>Lappnäsberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>721122.1109462137</v>
+        <v>721211</v>
       </c>
       <c r="R7" t="n">
-        <v>7074808.097173669</v>
+        <v>7074776</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1380,22 +1284,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-05-18</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-05-18</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,90 +1310,61 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Carl Jansson, Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>100976998</v>
+        <v>100976994</v>
       </c>
       <c r="B8" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lappnäsholmen, Hummelholm, Nordmaling, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>721205.7349319386</v>
+        <v>721052</v>
       </c>
       <c r="R8" t="n">
-        <v>7074764.203716364</v>
+        <v>7074837</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1519,21 +1394,11 @@
           <t>2022-05-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-05-18</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1542,6 +1407,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1562,49 +1442,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133342615</v>
+        <v>100976995</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lappnäsholmen, Ång</t>
+          <t>Lappnäsholmen, Hummelholm, Nordmaling, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>721153</v>
+        <v>721122</v>
       </c>
       <c r="R9" t="n">
-        <v>7074780</v>
+        <v>7074808</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1631,17 +1507,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1652,64 +1523,92 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Carl Jansson, Emil Larsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133342617</v>
+        <v>59474108</v>
       </c>
       <c r="B10" t="n">
-        <v>91987</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lappnäsholmen, Ång</t>
+          <t>Hummelholm, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721192</v>
+        <v>721011</v>
       </c>
       <c r="R10" t="n">
         <v>7074785</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1733,12 +1632,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2016-04-21</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2016-04-21</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1753,43 +1662,39 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133342616</v>
+        <v>100976997</v>
       </c>
       <c r="B11" t="n">
-        <v>57153</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1798,16 +1703,21 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lappnäsholmen, Ång</t>
+          <t>Lappnäsholmen, Hummelholm, Nordmaling, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>721200</v>
+        <v>721205</v>
       </c>
       <c r="R11" t="n">
-        <v>7074758</v>
+        <v>7074763</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1834,17 +1744,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färsk spillning</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1859,48 +1764,48 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Carl Jansson, Emil Larsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133210653</v>
+        <v>133210656</v>
       </c>
       <c r="B12" t="n">
-        <v>91967</v>
+        <v>57972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1910,13 +1815,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721113</v>
+        <v>721193</v>
       </c>
       <c r="R12" t="n">
-        <v>7074774</v>
+        <v>7074784</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1945,7 +1850,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1955,7 +1860,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1982,10 +1887,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133210656</v>
+        <v>133210651</v>
       </c>
       <c r="B13" t="n">
-        <v>57972</v>
+        <v>57975</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,16 +1898,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2011,19 +1916,27 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lappnäsberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>721193</v>
+        <v>721116</v>
       </c>
       <c r="R13" t="n">
-        <v>7074784</v>
+        <v>7074774</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2052,7 +1965,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2062,7 +1975,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>4,5 cm stort i diameter vilket stämmer bra överens med måttet på bohål för tretåig hackspett</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2089,48 +2007,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133210654</v>
+        <v>133342615</v>
       </c>
       <c r="B14" t="n">
-        <v>92399</v>
+        <v>57975</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lappnäsberget, Ång</t>
+          <t>Lappnäsholmen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721028</v>
+        <v>721153</v>
       </c>
       <c r="R14" t="n">
-        <v>7074796</v>
+        <v>7074780</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2157,19 +2079,14 @@
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:44</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,60 +2101,69 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133210655</v>
+        <v>100976998</v>
       </c>
       <c r="B15" t="n">
-        <v>91967</v>
+        <v>57132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lappnäsberget, Ång</t>
+          <t>Lappnäsholmen, Hummelholm, Nordmaling, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721025</v>
+        <v>721206</v>
       </c>
       <c r="R15" t="n">
-        <v>7074794</v>
+        <v>7074764</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2261,22 +2187,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:45</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:45</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,56 +2207,64 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Carl Jansson, Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133210658</v>
+        <v>133342616</v>
       </c>
       <c r="B16" t="n">
-        <v>91987</v>
+        <v>57153</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lappnäsberget, Ång</t>
+          <t>Lappnäsholmen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721193</v>
+        <v>721200</v>
       </c>
       <c r="R16" t="n">
-        <v>7074784</v>
+        <v>7074758</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2367,19 +2291,14 @@
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:02</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färsk spillning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,60 +2313,73 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133210660</v>
+        <v>101945155</v>
       </c>
       <c r="B17" t="n">
-        <v>91967</v>
+        <v>56876</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>208257</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lappnäsberget, Ång</t>
+          <t>Skogsväg, Hummelholm, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721211</v>
+        <v>721180</v>
       </c>
       <c r="R17" t="n">
-        <v>7074788</v>
+        <v>7074816</v>
       </c>
       <c r="S17" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2471,22 +2403,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2022-06-27</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2022-06-27</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2495,248 +2427,22 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>133210651</v>
-      </c>
-      <c r="B18" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Lappnäsberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>721116</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7074774</v>
-      </c>
-      <c r="S18" t="n">
-        <v>48</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>4,5 cm stort i diameter vilket stämmer bra överens med måttet på bohål för tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>133210659</v>
-      </c>
-      <c r="B19" t="n">
-        <v>92399</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Hermanssonia centrifuga</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Lappnäsberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>721211</v>
-      </c>
-      <c r="R19" t="n">
-        <v>7074776</v>
-      </c>
-      <c r="S19" t="n">
-        <v>14</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20163-2026 artfynd.xlsx
+++ b/artfynd/A 20163-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100976996</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133210653</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133210655</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133210660</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1216,6 +1241,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133210654</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133210659</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1439,6 +1474,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100976994</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1555,6 +1595,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100976995</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,6 +1716,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59474108</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1777,6 +1827,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100976997</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1884,6 +1939,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133210656</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2004,6 +2064,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133210651</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2114,6 +2179,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133342615</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2220,6 +2290,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100976998</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2324,6 +2399,11 @@
       <c r="AY16" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133342616</t>
         </is>
       </c>
     </row>
@@ -2443,8 +2523,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101945155</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>